--- a/data/trans_orig/P19C02-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P19C02-Provincia-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2007</t>
+          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2007 (tasa de respuesta: 99,9%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>48189</t>
+          <t>50074</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>73935</t>
+          <t>75711</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>26,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>38,61%</t>
+          <t>39,54%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56992</t>
+          <t>56994</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>85209</t>
+          <t>84794</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,35%</t>
+          <t>42,14%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>113150</t>
+          <t>114130</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>152679</t>
+          <t>153396</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>29,06%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>39,06%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>117558</t>
+          <t>115782</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>143304</t>
+          <t>141419</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>61,39%</t>
+          <t>60,46%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>73,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>116013</t>
+          <t>116428</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>144230</t>
+          <t>144228</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,65%</t>
+          <t>57,86%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>240037</t>
+          <t>239320</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>279566</t>
+          <t>278586</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>60,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>70,94%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>88793</t>
+          <t>87298</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>125774</t>
+          <t>123690</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,3%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,69%</t>
+          <t>30,19%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>99444</t>
+          <t>101204</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>136870</t>
+          <t>139266</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,59%</t>
+          <t>22,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>197465</t>
+          <t>196190</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>249975</t>
+          <t>250046</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>29,42%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>283982</t>
+          <t>286066</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>320963</t>
+          <t>322458</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,31%</t>
+          <t>69,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,7%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>303350</t>
+          <t>300954</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>340776</t>
+          <t>339016</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>600002</t>
+          <t>599931</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>652512</t>
+          <t>653787</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,92%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>58954</t>
+          <t>57530</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86957</t>
+          <t>87434</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,92%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>36,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>59576</t>
+          <t>61226</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>89319</t>
+          <t>90460</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>21,2%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>125795</t>
+          <t>125126</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>167415</t>
+          <t>170290</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>23,82%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>32,41%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>149580</t>
+          <t>149103</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>177583</t>
+          <t>179007</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,24%</t>
+          <t>63,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,08%</t>
+          <t>75,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>199487</t>
+          <t>198346</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>229230</t>
+          <t>227580</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>68,68%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>78,8%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>357928</t>
+          <t>355053</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>399548</t>
+          <t>400217</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,13%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>76,18%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>65068</t>
+          <t>64763</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>95441</t>
+          <t>94150</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,21%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71543</t>
+          <t>72490</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>102988</t>
+          <t>101290</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,88%</t>
+          <t>24,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>33,82%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>145576</t>
+          <t>145478</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>186820</t>
+          <t>188059</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>25,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,95%</t>
+          <t>33,16%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>172090</t>
+          <t>173381</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>202463</t>
+          <t>202768</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>64,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,79%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>196546</t>
+          <t>198244</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>227991</t>
+          <t>227044</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>66,18%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,12%</t>
+          <t>75,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>380245</t>
+          <t>379006</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>421489</t>
+          <t>421587</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>67,05%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,33%</t>
+          <t>74,35%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25847</t>
+          <t>25281</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45641</t>
+          <t>45790</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>15,18%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,8%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>31598</t>
+          <t>32051</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>54473</t>
+          <t>55248</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,77%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>64110</t>
+          <t>62774</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>92657</t>
+          <t>93187</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>27,07%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>124637</t>
+          <t>124488</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>144431</t>
+          <t>144997</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,2%</t>
+          <t>73,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>85,15%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>119433</t>
+          <t>118658</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142308</t>
+          <t>141855</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,23%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>81,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>251527</t>
+          <t>250997</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>280074</t>
+          <t>281410</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>72,93%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,37%</t>
+          <t>81,76%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54359</t>
+          <t>55091</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81018</t>
+          <t>81224</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>28,72%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,81%</t>
+          <t>42,91%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>54808</t>
+          <t>53247</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>81822</t>
+          <t>81356</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,94%</t>
+          <t>26,17%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>39,98%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>115644</t>
+          <t>115679</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>153865</t>
+          <t>154427</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,18%</t>
+          <t>39,32%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>108252</t>
+          <t>108046</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>134911</t>
+          <t>134179</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,19%</t>
+          <t>57,09%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>71,28%</t>
+          <t>70,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>121649</t>
+          <t>122115</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>148663</t>
+          <t>150224</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>60,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,06%</t>
+          <t>73,83%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>238876</t>
+          <t>238314</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>277097</t>
+          <t>277062</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,7 +2646,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,82%</t>
+          <t>60,68%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>105550</t>
+          <t>104846</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>145023</t>
+          <t>144942</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,23%</t>
+          <t>31,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>116889</t>
+          <t>118335</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>157720</t>
+          <t>160071</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,94%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>29,68%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>233193</t>
+          <t>232559</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>289148</t>
+          <t>289365</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,23%</t>
+          <t>23,17%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,81%</t>
+          <t>28,83%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>319302</t>
+          <t>319383</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>358775</t>
+          <t>359479</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,77%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>77,27%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>381648</t>
+          <t>379297</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>422479</t>
+          <t>421033</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>70,32%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,06%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>714544</t>
+          <t>714327</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>770499</t>
+          <t>771133</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>71,19%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,77%</t>
+          <t>76,83%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>136241</t>
+          <t>138724</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>180472</t>
+          <t>179196</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>25,92%</t>
+          <t>26,4%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>181257</t>
+          <t>178809</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>225154</t>
+          <t>224546</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,64%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,07%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>326544</t>
+          <t>328834</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>389922</t>
+          <t>392035</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,44%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,1%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>345080</t>
+          <t>346356</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>389311</t>
+          <t>386828</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>74,08%</t>
+          <t>73,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>366327</t>
+          <t>366935</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>410224</t>
+          <t>412672</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,36%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>727110</t>
+          <t>724997</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>790488</t>
+          <t>788198</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>64,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,56%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>660275</t>
+          <t>658676</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>751819</t>
+          <t>746373</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26,9%</t>
+          <t>26,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>30,41%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>754103</t>
+          <t>747514</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>843476</t>
+          <t>844575</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,54%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,85%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1431757</t>
+          <t>1434830</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1566168</t>
+          <t>1562899</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,1%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1702923</t>
+          <t>1708369</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1794467</t>
+          <t>1796066</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>69,37%</t>
+          <t>69,59%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>73,1%</t>
+          <t>73,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1894533</t>
+          <t>1893434</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1983906</t>
+          <t>1990495</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>69,19%</t>
+          <t>69,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>72,46%</t>
+          <t>72,7%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3626582</t>
+          <t>3629851</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3760993</t>
+          <t>3757920</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>69,84%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,37%</t>
         </is>
       </c>
     </row>
@@ -3861,7 +3861,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2012</t>
+          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2012 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>50257</t>
+          <t>49319</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>77753</t>
+          <t>77420</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>19,68%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,03%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51984</t>
+          <t>51077</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>81171</t>
+          <t>79350</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,69%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>31,59%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>110115</t>
+          <t>108727</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>150795</t>
+          <t>148851</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>29,66%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>172807</t>
+          <t>173140</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>200303</t>
+          <t>201241</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>69,1%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,94%</t>
+          <t>80,32%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>170049</t>
+          <t>171870</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>199236</t>
+          <t>200143</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,31%</t>
+          <t>79,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>350985</t>
+          <t>352929</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>391665</t>
+          <t>393053</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>69,95%</t>
+          <t>70,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>78,33%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>76148</t>
+          <t>77179</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>111388</t>
+          <t>113850</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>27,48%</t>
+          <t>28,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>105653</t>
+          <t>106711</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>145884</t>
+          <t>146035</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,13%</t>
+          <t>24,37%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>33,35%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>193064</t>
+          <t>194637</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>245373</t>
+          <t>246858</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,1%</t>
+          <t>29,28%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>293894</t>
+          <t>291432</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>329134</t>
+          <t>328103</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>72,52%</t>
+          <t>71,91%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>80,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>291939</t>
+          <t>291788</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>332170</t>
+          <t>331112</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,87%</t>
+          <t>75,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>597732</t>
+          <t>596247</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>650041</t>
+          <t>648468</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,9%</t>
+          <t>70,72%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>76,91%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>56551</t>
+          <t>57236</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86542</t>
+          <t>87037</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,32%</t>
+          <t>19,56%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,74%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>82860</t>
+          <t>82716</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>117232</t>
+          <t>117613</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,2%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,66%</t>
+          <t>35,78%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>146704</t>
+          <t>149149</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>193589</t>
+          <t>191417</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>30,8%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>206130</t>
+          <t>205635</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>236121</t>
+          <t>235436</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,26%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,68%</t>
+          <t>80,44%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>211520</t>
+          <t>211139</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>245892</t>
+          <t>246036</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,34%</t>
+          <t>64,22%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,8%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>427835</t>
+          <t>430007</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>474720</t>
+          <t>472275</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>68,85%</t>
+          <t>69,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,39%</t>
+          <t>76,0%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75997</t>
+          <t>75593</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>108953</t>
+          <t>110124</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,27%</t>
+          <t>24,15%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>35,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>87971</t>
+          <t>86194</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>123548</t>
+          <t>121332</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,66%</t>
+          <t>25,14%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,04%</t>
+          <t>35,39%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>171038</t>
+          <t>173880</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>219839</t>
+          <t>223034</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>34,0%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>204124</t>
+          <t>202953</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>237080</t>
+          <t>237484</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,73%</t>
+          <t>75,85%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>219267</t>
+          <t>221483</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>254844</t>
+          <t>256621</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>63,96%</t>
+          <t>64,61%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,34%</t>
+          <t>74,86%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>436052</t>
+          <t>432857</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>484853</t>
+          <t>482011</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,49%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>32988</t>
+          <t>33459</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>56329</t>
+          <t>57257</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,18%</t>
+          <t>17,42%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,33%</t>
+          <t>29,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42912</t>
+          <t>42430</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67478</t>
+          <t>67468</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,05%</t>
+          <t>21,81%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,68%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>81199</t>
+          <t>82922</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>117305</t>
+          <t>115763</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,0%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>29,94%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>135729</t>
+          <t>134801</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>159070</t>
+          <t>158599</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,67%</t>
+          <t>70,19%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,82%</t>
+          <t>82,58%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>127104</t>
+          <t>127114</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>151670</t>
+          <t>152152</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,32%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>77,95%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>269335</t>
+          <t>270877</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>305441</t>
+          <t>303718</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>70,06%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>79,0%</t>
+          <t>78,55%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>62890</t>
+          <t>61477</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>92666</t>
+          <t>94063</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,59%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>37,63%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>56874</t>
+          <t>56727</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>85885</t>
+          <t>85236</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,48%</t>
+          <t>21,42%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,43%</t>
+          <t>32,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>127887</t>
+          <t>128030</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>169583</t>
+          <t>168369</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,84%</t>
+          <t>24,87%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,71%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>157307</t>
+          <t>155910</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>187083</t>
+          <t>188496</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>62,37%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>75,41%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>178945</t>
+          <t>179594</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>207956</t>
+          <t>208103</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,57%</t>
+          <t>67,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,52%</t>
+          <t>78,58%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>345220</t>
+          <t>346434</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>386916</t>
+          <t>386773</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,06%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,16%</t>
+          <t>75,13%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>137502</t>
+          <t>138788</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>178227</t>
+          <t>181847</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>23,95%</t>
+          <t>24,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>176613</t>
+          <t>175658</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>225082</t>
+          <t>224370</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,21%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,96%</t>
+          <t>35,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>328332</t>
+          <t>324334</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>391981</t>
+          <t>392241</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,36%</t>
+          <t>27,03%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,66%</t>
+          <t>32,68%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>395852</t>
+          <t>392232</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>436577</t>
+          <t>435291</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,95%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>75,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>400905</t>
+          <t>401617</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>449374</t>
+          <t>450329</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64,04%</t>
+          <t>64,16%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>71,79%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>808084</t>
+          <t>807824</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>871733</t>
+          <t>875731</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,34%</t>
+          <t>67,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,97%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>239052</t>
+          <t>241641</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>291848</t>
+          <t>291250</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>46,04%</t>
+          <t>45,95%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>238526</t>
+          <t>239914</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>292834</t>
+          <t>293906</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,7%</t>
+          <t>41,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>492916</t>
+          <t>495867</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>566101</t>
+          <t>565978</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>37,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,36%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>342057</t>
+          <t>342655</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>394853</t>
+          <t>392264</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>53,96%</t>
+          <t>54,05%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>409460</t>
+          <t>408388</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>463768</t>
+          <t>462380</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>58,3%</t>
+          <t>58,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>770098</t>
+          <t>770221</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>843283</t>
+          <t>840332</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,64%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>63,11%</t>
+          <t>62,89%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>810594</t>
+          <t>813097</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>914182</t>
+          <t>915239</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,84%</t>
+          <t>27,93%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>31,4%</t>
+          <t>31,43%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>935900</t>
+          <t>924557</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1040413</t>
+          <t>1035890</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,73%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1782601</t>
+          <t>1772288</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1927511</t>
+          <t>1921758</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,25%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,81%</t>
+          <t>31,71%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1997424</t>
+          <t>1996367</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2101012</t>
+          <t>2098509</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>68,6%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>72,16%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2107889</t>
+          <t>2112412</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2212402</t>
+          <t>2223745</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>67,1%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>70,27%</t>
+          <t>70,63%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4132397</t>
+          <t>4138150</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4277307</t>
+          <t>4287620</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>68,19%</t>
+          <t>68,29%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,75%</t>
         </is>
       </c>
     </row>
@@ -7184,7 +7184,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2016</t>
+          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44759</t>
+          <t>43901</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71965</t>
+          <t>71677</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,35%</t>
+          <t>29,23%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50340</t>
+          <t>50774</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>77886</t>
+          <t>78877</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,62%</t>
+          <t>32,02%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>102540</t>
+          <t>102227</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>144904</t>
+          <t>141266</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,86%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,48%</t>
+          <t>28,74%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>173253</t>
+          <t>173541</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>200459</t>
+          <t>201317</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,77%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>168448</t>
+          <t>167457</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>195994</t>
+          <t>195560</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,38%</t>
+          <t>67,98%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>346647</t>
+          <t>350285</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>389011</t>
+          <t>389324</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,52%</t>
+          <t>71,26%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,14%</t>
+          <t>79,2%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83420</t>
+          <t>85713</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>119912</t>
+          <t>119145</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>22,97%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,02%</t>
+          <t>32,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>116162</t>
+          <t>114942</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>153145</t>
+          <t>150897</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,53%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,94%</t>
+          <t>38,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>212355</t>
+          <t>208992</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>264086</t>
+          <t>260105</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>34,38%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>243253</t>
+          <t>244020</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>279745</t>
+          <t>277452</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,98%</t>
+          <t>67,19%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,03%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>240182</t>
+          <t>242430</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>277165</t>
+          <t>278385</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,06%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,47%</t>
+          <t>70,78%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>492406</t>
+          <t>496387</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>544137</t>
+          <t>547500</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,09%</t>
+          <t>65,62%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>71,93%</t>
+          <t>72,37%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53011</t>
+          <t>53295</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80095</t>
+          <t>80300</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,64%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>62800</t>
+          <t>63261</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>92499</t>
+          <t>95193</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,55%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,93%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>124890</t>
+          <t>121773</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>165409</t>
+          <t>164343</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,88%</t>
+          <t>20,35%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,65%</t>
+          <t>27,47%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>210412</t>
+          <t>210207</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>237496</t>
+          <t>237212</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,75%</t>
+          <t>81,65%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>215265</t>
+          <t>212571</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>244964</t>
+          <t>244503</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>69,07%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,59%</t>
+          <t>79,45%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>432861</t>
+          <t>433927</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>473380</t>
+          <t>476497</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,35%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,12%</t>
+          <t>79,65%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67335</t>
+          <t>67462</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>99618</t>
+          <t>99454</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,44%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,18%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71167</t>
+          <t>71994</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>105064</t>
+          <t>105046</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,64%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>30,11%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>147053</t>
+          <t>149282</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>195045</t>
+          <t>193354</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>28,48%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>230429</t>
+          <t>230593</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>262712</t>
+          <t>262585</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,82%</t>
+          <t>69,87%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,56%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>243797</t>
+          <t>243815</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>277694</t>
+          <t>276867</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,88%</t>
+          <t>69,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,36%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>483863</t>
+          <t>485554</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>531855</t>
+          <t>529626</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,34%</t>
+          <t>78,01%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69670</t>
+          <t>69259</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89747</t>
+          <t>89806</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,33%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>89641</t>
+          <t>89520</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>110795</t>
+          <t>111066</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,61%</t>
+          <t>61,53%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,15%</t>
+          <t>76,33%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>165612</t>
+          <t>166474</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>194637</t>
+          <t>196722</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,89%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>73,53%</t>
+          <t>74,31%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29475</t>
+          <t>29416</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>49552</t>
+          <t>49963</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,67%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,56%</t>
+          <t>41,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34705</t>
+          <t>34434</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>55859</t>
+          <t>55980</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,85%</t>
+          <t>23,67%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,39%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>70085</t>
+          <t>68000</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>99110</t>
+          <t>98248</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>26,47%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>37,11%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>42561</t>
+          <t>41812</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>69068</t>
+          <t>69076</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>18,22%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,56%</t>
+          <t>29,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>63910</t>
+          <t>63540</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>93633</t>
+          <t>93708</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,86%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>115557</t>
+          <t>112757</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>153902</t>
+          <t>153317</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,04%</t>
+          <t>23,45%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>31,89%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>164547</t>
+          <t>164539</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>191054</t>
+          <t>191803</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,44%</t>
+          <t>70,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>153504</t>
+          <t>153429</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>183227</t>
+          <t>183597</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>62,08%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,14%</t>
+          <t>74,29%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>326851</t>
+          <t>327436</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>365196</t>
+          <t>367996</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>68,11%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,96%</t>
+          <t>76,55%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>123368</t>
+          <t>121940</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>164263</t>
+          <t>163329</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,89%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>37,14%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>144836</t>
+          <t>145710</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>189876</t>
+          <t>187825</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,92%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,98%</t>
+          <t>38,56%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>279552</t>
+          <t>281393</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>337216</t>
+          <t>339273</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>30,28%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>36,51%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>278044</t>
+          <t>278978</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>318939</t>
+          <t>320367</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,11%</t>
+          <t>72,43%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>297175</t>
+          <t>299226</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>342215</t>
+          <t>341341</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>61,44%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>70,08%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>592142</t>
+          <t>590085</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>649806</t>
+          <t>647965</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>63,49%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,92%</t>
+          <t>69,72%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>315201</t>
+          <t>314079</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>366677</t>
+          <t>363338</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>49,23%</t>
+          <t>49,06%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>57,27%</t>
+          <t>56,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>331957</t>
+          <t>335949</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>388813</t>
+          <t>390471</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>48,02%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>663795</t>
+          <t>661181</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>738241</t>
+          <t>737249</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>49,85%</t>
+          <t>49,65%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>55,44%</t>
+          <t>55,37%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>273575</t>
+          <t>276914</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>325051</t>
+          <t>326173</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>42,73%</t>
+          <t>43,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>50,77%</t>
+          <t>50,94%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>302528</t>
+          <t>300870</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>359384</t>
+          <t>355392</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>51,98%</t>
+          <t>51,41%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>593352</t>
+          <t>594344</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>667798</t>
+          <t>670412</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>44,56%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>50,15%</t>
+          <t>50,35%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>879600</t>
+          <t>877134</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>976764</t>
+          <t>974335</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>36,57%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1009448</t>
+          <t>1011762</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1119982</t>
+          <t>1112294</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>35,21%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1919510</t>
+          <t>1924967</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2064428</t>
+          <t>2070108</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,12 +10208,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>34,7%</t>
+          <t>34,8%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>37,32%</t>
+          <t>37,42%</t>
         </is>
       </c>
     </row>
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1687569</t>
+          <t>1689998</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1784733</t>
+          <t>1787199</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>63,34%</t>
+          <t>63,43%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>66,99%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1747333</t>
+          <t>1755021</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1857867</t>
+          <t>1855553</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>64,79%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3467220</t>
+          <t>3461540</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3612138</t>
+          <t>3606681</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>62,68%</t>
+          <t>62,58%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>65,3%</t>
+          <t>65,2%</t>
         </is>
       </c>
     </row>
@@ -10507,7 +10507,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2023</t>
+          <t>Población según si el motivo por su última visita al dentista fue una limpieza de boca en 2023 (tasa de respuesta: 99,54%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10702,12 +10702,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>124753</t>
+          <t>123484</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>168271</t>
+          <t>166878</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10717,12 +10717,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,85%</t>
+          <t>40,43%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>55,09%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10737,12 +10737,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>116525</t>
+          <t>117461</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>146035</t>
+          <t>146205</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -10752,12 +10752,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>40,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,78%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10772,12 +10772,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>253001</t>
+          <t>251861</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>303767</t>
+          <t>304290</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -10787,12 +10787,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,66%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,22%</t>
+          <t>51,31%</t>
         </is>
       </c>
     </row>
@@ -10815,12 +10815,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>137159</t>
+          <t>138552</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>180677</t>
+          <t>181946</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -10830,12 +10830,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>45,36%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,15%</t>
+          <t>59,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10850,12 +10850,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>141572</t>
+          <t>141402</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>171082</t>
+          <t>170146</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -10865,12 +10865,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,22%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,48%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10885,12 +10885,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>289270</t>
+          <t>288747</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>340036</t>
+          <t>341176</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -10900,12 +10900,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,78%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,34%</t>
+          <t>57,53%</t>
         </is>
       </c>
     </row>
@@ -11045,12 +11045,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>162931</t>
+          <t>162301</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>224165</t>
+          <t>220625</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11060,12 +11060,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,14%</t>
+          <t>32,01%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,22%</t>
+          <t>43,52%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11080,12 +11080,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>158922</t>
+          <t>158915</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>197382</t>
+          <t>197814</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11095,12 +11095,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>31,68%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11115,12 +11115,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>331690</t>
+          <t>332627</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>404453</t>
+          <t>405496</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11130,12 +11130,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,89%</t>
+          <t>32,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>40,21%</t>
         </is>
       </c>
     </row>
@@ -11158,12 +11158,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>282819</t>
+          <t>286359</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>344053</t>
+          <t>344683</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -11173,12 +11173,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,78%</t>
+          <t>56,48%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,86%</t>
+          <t>67,99%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11193,12 +11193,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>304166</t>
+          <t>303734</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>342626</t>
+          <t>342633</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -11208,12 +11208,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>60,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,31%</t>
+          <t>68,32%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11228,12 +11228,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>604079</t>
+          <t>603036</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>676842</t>
+          <t>675905</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -11243,12 +11243,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,9%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>67,02%</t>
         </is>
       </c>
     </row>
@@ -11388,12 +11388,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57347</t>
+          <t>57661</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>86562</t>
+          <t>85947</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11403,12 +11403,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11423,12 +11423,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>76432</t>
+          <t>76415</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>105020</t>
+          <t>106582</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11438,12 +11438,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,8%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>139815</t>
+          <t>140875</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>181703</t>
+          <t>182322</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11473,12 +11473,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,0%</t>
+          <t>22,17%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,59%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -11501,12 +11501,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>213665</t>
+          <t>214280</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>242880</t>
+          <t>242566</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11536,12 +11536,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>230255</t>
+          <t>228693</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>258843</t>
+          <t>258860</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11551,12 +11551,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>453799</t>
+          <t>453180</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>495687</t>
+          <t>494627</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11586,12 +11586,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,41%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,0%</t>
+          <t>77,83%</t>
         </is>
       </c>
     </row>
@@ -11731,12 +11731,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>132833</t>
+          <t>134519</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>176730</t>
+          <t>178966</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>42,83%</t>
+          <t>43,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>56,99%</t>
+          <t>57,71%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11766,12 +11766,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>109100</t>
+          <t>108972</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>224276</t>
+          <t>223590</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -11781,12 +11781,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>47,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11801,12 +11801,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>238260</t>
+          <t>240616</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>382715</t>
+          <t>384655</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -11816,12 +11816,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>49,09%</t>
         </is>
       </c>
     </row>
@@ -11844,12 +11844,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>133390</t>
+          <t>131154</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>177287</t>
+          <t>175601</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -11859,12 +11859,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>42,29%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>57,17%</t>
+          <t>56,62%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11879,12 +11879,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>249189</t>
+          <t>249875</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>364365</t>
+          <t>364493</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -11894,12 +11894,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>52,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11914,12 +11914,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>400870</t>
+          <t>398930</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>545325</t>
+          <t>542969</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -11929,12 +11929,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>51,16%</t>
+          <t>50,91%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,29%</t>
         </is>
       </c>
     </row>
@@ -12074,12 +12074,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>139340</t>
+          <t>139221</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>152253</t>
+          <t>152903</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12089,12 +12089,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,73%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,4%</t>
+          <t>90,78%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12109,12 +12109,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>170397</t>
+          <t>171056</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>183584</t>
+          <t>183979</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -12124,12 +12124,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>84,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,75%</t>
+          <t>90,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12144,12 +12144,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>315286</t>
+          <t>315087</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>334024</t>
+          <t>334087</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -12159,12 +12159,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,12%</t>
         </is>
       </c>
     </row>
@@ -12187,12 +12187,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>16176</t>
+          <t>15526</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29089</t>
+          <t>29208</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12202,12 +12202,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,6%</t>
+          <t>9,22%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12222,12 +12222,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18708</t>
+          <t>18313</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31895</t>
+          <t>31236</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12237,12 +12237,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>15,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12257,12 +12257,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36697</t>
+          <t>36634</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55435</t>
+          <t>55634</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12272,12 +12272,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,01%</t>
         </is>
       </c>
     </row>
@@ -12417,12 +12417,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>35043</t>
+          <t>34420</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>58124</t>
+          <t>57832</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12432,12 +12432,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,81%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,91%</t>
+          <t>22,79%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12452,12 +12452,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>39128</t>
+          <t>40466</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>60890</t>
+          <t>59720</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12467,12 +12467,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,88%</t>
+          <t>16,43%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12487,12 +12487,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>81021</t>
+          <t>79594</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>111240</t>
+          <t>111751</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12502,12 +12502,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,2%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,24%</t>
+          <t>22,35%</t>
         </is>
       </c>
     </row>
@@ -12530,12 +12530,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>195608</t>
+          <t>195900</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>218689</t>
+          <t>219312</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12545,12 +12545,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,09%</t>
+          <t>77,21%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,43%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12565,12 +12565,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>185460</t>
+          <t>186630</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>207222</t>
+          <t>205884</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12580,12 +12580,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,28%</t>
+          <t>75,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,12%</t>
+          <t>83,57%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12600,12 +12600,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>388842</t>
+          <t>388331</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>419061</t>
+          <t>420488</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12615,12 +12615,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,76%</t>
+          <t>77,65%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>84,08%</t>
         </is>
       </c>
     </row>
@@ -12760,12 +12760,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>253149</t>
+          <t>253688</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>311258</t>
+          <t>311207</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -12775,12 +12775,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,84%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12795,12 +12795,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>375066</t>
+          <t>375999</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>677838</t>
+          <t>682808</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -12810,12 +12810,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,39%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>81,83%</t>
+          <t>82,43%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12830,12 +12830,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>651926</t>
+          <t>656983</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1026997</t>
+          <t>1022653</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -12845,12 +12845,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,63%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,88%</t>
+          <t>71,58%</t>
         </is>
       </c>
     </row>
@@ -12873,12 +12873,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>289141</t>
+          <t>289192</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>347250</t>
+          <t>346711</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -12888,12 +12888,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>48,16%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12908,12 +12908,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>150527</t>
+          <t>145557</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>453299</t>
+          <t>452366</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -12923,12 +12923,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>18,17%</t>
+          <t>17,57%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>54,61%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12943,12 +12943,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>401768</t>
+          <t>406112</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>776839</t>
+          <t>771782</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -12958,12 +12958,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,37%</t>
+          <t>54,02%</t>
         </is>
       </c>
     </row>
@@ -13103,12 +13103,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>177180</t>
+          <t>196693</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>585836</t>
+          <t>586079</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13118,12 +13118,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,5%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13138,12 +13138,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>463671</t>
+          <t>464060</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>507030</t>
+          <t>506712</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13153,12 +13153,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>65,87%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>72,03%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13173,12 +13173,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>508597</t>
+          <t>572801</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1079836</t>
+          <t>1078453</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13188,12 +13188,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>31,54%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>66,96%</t>
+          <t>66,88%</t>
         </is>
       </c>
     </row>
@@ -13216,12 +13216,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>322803</t>
+          <t>322560</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>731459</t>
+          <t>711946</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13231,12 +13231,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,5%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>78,35%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13251,12 +13251,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>196894</t>
+          <t>197212</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>240253</t>
+          <t>239864</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13266,12 +13266,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,02%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>34,13%</t>
+          <t>34,08%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13286,12 +13286,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>532727</t>
+          <t>534110</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1103966</t>
+          <t>1039762</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13301,12 +13301,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>33,04%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>68,46%</t>
+          <t>64,48%</t>
         </is>
       </c>
     </row>
@@ -13446,12 +13446,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1134610</t>
+          <t>1140942</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1595896</t>
+          <t>1588859</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13461,12 +13461,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>33,83%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>47,58%</t>
+          <t>47,37%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13481,12 +13481,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1646831</t>
+          <t>1639898</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2130632</t>
+          <t>2089353</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13496,12 +13496,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>46,02%</t>
+          <t>45,82%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>58,38%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13516,12 +13516,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2905594</t>
+          <t>2925284</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3533389</t>
+          <t>3527322</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13531,12 +13531,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>42,19%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>50,97%</t>
+          <t>50,88%</t>
         </is>
       </c>
     </row>
@@ -13559,12 +13559,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1758064</t>
+          <t>1765101</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2219350</t>
+          <t>2213018</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13574,12 +13574,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>52,42%</t>
+          <t>52,63%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>66,17%</t>
+          <t>65,98%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13594,12 +13594,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1448195</t>
+          <t>1489474</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1931996</t>
+          <t>1938929</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13609,12 +13609,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>41,62%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>53,98%</t>
+          <t>54,18%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13629,12 +13629,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3399398</t>
+          <t>3405465</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4027193</t>
+          <t>4007503</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13644,12 +13644,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>49,03%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>57,81%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C02-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P19C02-Provincia-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>50074</t>
+          <t>50256</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>75711</t>
+          <t>75219</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,15%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>39,54%</t>
+          <t>39,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>56994</t>
+          <t>57158</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>84794</t>
+          <t>84364</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>28,32%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>41,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>114130</t>
+          <t>114429</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>153396</t>
+          <t>150660</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>38,36%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>115782</t>
+          <t>116274</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>141419</t>
+          <t>141237</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>60,46%</t>
+          <t>60,72%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,85%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>116428</t>
+          <t>116858</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>144228</t>
+          <t>144064</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,86%</t>
+          <t>58,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>239320</t>
+          <t>242056</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>278586</t>
+          <t>278287</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>70,86%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>87298</t>
+          <t>88368</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>123690</t>
+          <t>123878</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,19%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>101204</t>
+          <t>100953</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>139266</t>
+          <t>138599</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,99%</t>
+          <t>22,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,64%</t>
+          <t>31,48%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>196190</t>
+          <t>198722</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>250046</t>
+          <t>249455</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,08%</t>
+          <t>23,38%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,42%</t>
+          <t>29,35%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>286066</t>
+          <t>285878</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>322458</t>
+          <t>321388</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,81%</t>
+          <t>69,77%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,7%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>300954</t>
+          <t>301621</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>339016</t>
+          <t>339267</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>77,01%</t>
+          <t>77,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>599931</t>
+          <t>600522</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>653787</t>
+          <t>651255</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,58%</t>
+          <t>70,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,92%</t>
+          <t>76,62%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57530</t>
+          <t>58588</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87434</t>
+          <t>88592</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>24,32%</t>
+          <t>24,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>37,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>61226</t>
+          <t>59803</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>90460</t>
+          <t>89787</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,2%</t>
+          <t>20,71%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>125126</t>
+          <t>127328</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>170290</t>
+          <t>168003</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>23,82%</t>
+          <t>24,24%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>32,41%</t>
+          <t>31,98%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>149103</t>
+          <t>147945</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>179007</t>
+          <t>177949</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,04%</t>
+          <t>62,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>75,68%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>198346</t>
+          <t>199019</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>227580</t>
+          <t>229003</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,68%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,8%</t>
+          <t>79,29%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>355053</t>
+          <t>357340</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>400217</t>
+          <t>398015</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>67,59%</t>
+          <t>68,02%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,18%</t>
+          <t>75,76%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64763</t>
+          <t>65337</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>94150</t>
+          <t>94414</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,21%</t>
+          <t>24,42%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,19%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>72490</t>
+          <t>71252</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>101290</t>
+          <t>102409</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>24,2%</t>
+          <t>23,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>33,82%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>145478</t>
+          <t>145619</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>188059</t>
+          <t>189128</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,65%</t>
+          <t>25,68%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>33,35%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>173381</t>
+          <t>173117</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>202768</t>
+          <t>202194</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,81%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,79%</t>
+          <t>75,58%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>198244</t>
+          <t>197125</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>227044</t>
+          <t>228282</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>66,18%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>75,8%</t>
+          <t>76,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>379006</t>
+          <t>377937</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>421587</t>
+          <t>421446</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>66,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>74,35%</t>
+          <t>74,32%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>25281</t>
+          <t>26154</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>45790</t>
+          <t>45185</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>15,36%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>32051</t>
+          <t>30836</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>55248</t>
+          <t>54699</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>18,43%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>31,77%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62774</t>
+          <t>62622</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>93187</t>
+          <t>93531</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>18,24%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>27,07%</t>
+          <t>27,17%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>124488</t>
+          <t>125093</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>144997</t>
+          <t>144124</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>73,11%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>84,64%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>118658</t>
+          <t>119207</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>141855</t>
+          <t>143070</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>68,23%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>81,57%</t>
+          <t>82,27%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>250997</t>
+          <t>250653</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>281410</t>
+          <t>281562</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>72,93%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>81,76%</t>
+          <t>81,81%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>55091</t>
+          <t>54630</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>81224</t>
+          <t>80324</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>29,11%</t>
+          <t>28,86%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>42,91%</t>
+          <t>42,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,12 +2483,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>53247</t>
+          <t>55526</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>81356</t>
+          <t>81900</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2498,12 +2498,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>26,17%</t>
+          <t>27,29%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>39,98%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>115679</t>
+          <t>115367</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>154427</t>
+          <t>153814</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>29,45%</t>
+          <t>29,37%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,32%</t>
+          <t>39,16%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>108046</t>
+          <t>108946</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>134179</t>
+          <t>134640</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>57,09%</t>
+          <t>57,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>122115</t>
+          <t>121571</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>150224</t>
+          <t>147945</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2611,12 +2611,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>60,02%</t>
+          <t>59,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>73,83%</t>
+          <t>72,71%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>238314</t>
+          <t>238927</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>277062</t>
+          <t>277374</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,68%</t>
+          <t>60,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>70,55%</t>
+          <t>70,63%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>104846</t>
+          <t>104841</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>144942</t>
+          <t>142364</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2811,7 +2811,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,22%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>118335</t>
+          <t>119216</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>160071</t>
+          <t>158458</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2841,12 +2841,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,1%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>29,68%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>232559</t>
+          <t>233973</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>289365</t>
+          <t>289734</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>23,17%</t>
+          <t>23,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>28,87%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>319383</t>
+          <t>321961</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>359479</t>
+          <t>359484</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,78%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2939,12 +2939,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>379297</t>
+          <t>380910</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>421033</t>
+          <t>420152</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,12 +2954,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>70,32%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>78,06%</t>
+          <t>77,9%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>714327</t>
+          <t>713958</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>771133</t>
+          <t>769719</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>71,13%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>76,83%</t>
+          <t>76,69%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>138724</t>
+          <t>137069</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>179196</t>
+          <t>177949</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>26,4%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>34,1%</t>
+          <t>33,86%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>178809</t>
+          <t>178383</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>224546</t>
+          <t>223094</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>30,23%</t>
+          <t>30,16%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>328834</t>
+          <t>325166</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>392035</t>
+          <t>388542</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>29,44%</t>
+          <t>29,11%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>34,78%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>346356</t>
+          <t>347603</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>386828</t>
+          <t>388483</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>65,9%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>73,6%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>366935</t>
+          <t>368387</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>412672</t>
+          <t>413098</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>69,77%</t>
+          <t>69,84%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>724997</t>
+          <t>728490</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>788198</t>
+          <t>791866</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>70,56%</t>
+          <t>70,89%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>658676</t>
+          <t>659841</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>746373</t>
+          <t>748681</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>26,83%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,5%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>747514</t>
+          <t>752463</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>844575</t>
+          <t>845461</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>27,3%</t>
+          <t>27,48%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>30,88%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1434830</t>
+          <t>1433902</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1562899</t>
+          <t>1560556</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,61%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>30,1%</t>
+          <t>30,05%</t>
         </is>
       </c>
     </row>
@@ -3590,12 +3590,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1708369</t>
+          <t>1706061</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1796066</t>
+          <t>1794901</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>69,59%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>73,17%</t>
+          <t>73,12%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1893434</t>
+          <t>1892548</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1990495</t>
+          <t>1985546</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>69,12%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>72,7%</t>
+          <t>72,52%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3629851</t>
+          <t>3632194</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3757920</t>
+          <t>3758848</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3675,12 +3675,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>69,9%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,39%</t>
         </is>
       </c>
     </row>
@@ -4056,12 +4056,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>49319</t>
+          <t>49191</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>77420</t>
+          <t>77240</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4071,12 +4071,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>19,68%</t>
+          <t>19,63%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>30,9%</t>
+          <t>30,83%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4091,12 +4091,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>51077</t>
+          <t>52057</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>79350</t>
+          <t>81711</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4106,12 +4106,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>31,59%</t>
+          <t>32,53%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4126,12 +4126,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>108727</t>
+          <t>108637</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>148851</t>
+          <t>148676</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4141,12 +4141,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>21,67%</t>
+          <t>21,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>29,66%</t>
+          <t>29,63%</t>
         </is>
       </c>
     </row>
@@ -4169,12 +4169,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>173140</t>
+          <t>173320</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>201241</t>
+          <t>201369</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4184,12 +4184,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>69,1%</t>
+          <t>69,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>80,32%</t>
+          <t>80,37%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4204,12 +4204,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>171870</t>
+          <t>169509</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>200143</t>
+          <t>199163</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4219,12 +4219,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>68,41%</t>
+          <t>67,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>79,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4239,12 +4239,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>352929</t>
+          <t>353104</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>393053</t>
+          <t>393143</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>70,34%</t>
+          <t>70,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>78,33%</t>
+          <t>78,35%</t>
         </is>
       </c>
     </row>
@@ -4399,12 +4399,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77179</t>
+          <t>76429</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>113850</t>
+          <t>114433</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4414,12 +4414,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>18,86%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4434,12 +4434,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>106711</t>
+          <t>105507</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>146035</t>
+          <t>144896</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4449,12 +4449,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>24,37%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,35%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4469,12 +4469,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>194637</t>
+          <t>192641</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>246858</t>
+          <t>243482</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4484,12 +4484,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,09%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,28%</t>
+          <t>28,88%</t>
         </is>
       </c>
     </row>
@@ -4512,12 +4512,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>291432</t>
+          <t>290849</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>328103</t>
+          <t>328853</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4527,12 +4527,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,76%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>81,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4547,12 +4547,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>291788</t>
+          <t>292927</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>331112</t>
+          <t>332316</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4562,12 +4562,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>66,65%</t>
+          <t>66,91%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,63%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4582,12 +4582,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>596247</t>
+          <t>599623</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>648468</t>
+          <t>650464</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4597,12 +4597,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>70,72%</t>
+          <t>71,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,91%</t>
+          <t>77,15%</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4742,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57236</t>
+          <t>55954</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>87037</t>
+          <t>85709</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>19,12%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>29,74%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4777,12 +4777,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>82716</t>
+          <t>83484</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>117613</t>
+          <t>117088</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4792,12 +4792,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>25,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,78%</t>
+          <t>35,62%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4812,12 +4812,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>149149</t>
+          <t>148690</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>191417</t>
+          <t>195763</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4827,12 +4827,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>30,8%</t>
+          <t>31,5%</t>
         </is>
       </c>
     </row>
@@ -4855,12 +4855,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>205635</t>
+          <t>206963</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>235436</t>
+          <t>236718</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4870,12 +4870,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,26%</t>
+          <t>70,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,44%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4890,12 +4890,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>211139</t>
+          <t>211664</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>246036</t>
+          <t>245268</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4905,12 +4905,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,38%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>74,84%</t>
+          <t>74,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4925,12 +4925,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>430007</t>
+          <t>425661</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>472275</t>
+          <t>472734</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4940,12 +4940,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>69,2%</t>
+          <t>68,5%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>76,07%</t>
         </is>
       </c>
     </row>
@@ -5085,12 +5085,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>75593</t>
+          <t>77075</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>110124</t>
+          <t>109598</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5100,12 +5100,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,15%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>35,17%</t>
+          <t>35,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5120,12 +5120,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>86194</t>
+          <t>87657</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>121332</t>
+          <t>120923</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5135,12 +5135,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,14%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5155,12 +5155,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>173880</t>
+          <t>172112</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>223034</t>
+          <t>220013</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5170,12 +5170,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,54%</t>
         </is>
       </c>
     </row>
@@ -5198,12 +5198,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>202953</t>
+          <t>203479</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>237484</t>
+          <t>236002</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5213,12 +5213,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>64,83%</t>
+          <t>64,99%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>75,85%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5233,12 +5233,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>221483</t>
+          <t>221892</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>256621</t>
+          <t>255158</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5248,12 +5248,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>64,61%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>74,86%</t>
+          <t>74,43%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5268,12 +5268,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>432857</t>
+          <t>435878</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>482011</t>
+          <t>483779</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5283,12 +5283,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>66,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,49%</t>
+          <t>73,76%</t>
         </is>
       </c>
     </row>
@@ -5428,12 +5428,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>33459</t>
+          <t>32817</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>57257</t>
+          <t>57806</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5443,12 +5443,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>17,42%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>29,81%</t>
+          <t>30,1%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5463,12 +5463,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>42430</t>
+          <t>44908</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67468</t>
+          <t>68955</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5478,12 +5478,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>21,81%</t>
+          <t>23,08%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>35,44%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5498,12 +5498,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>82922</t>
+          <t>83210</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>115763</t>
+          <t>118034</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5513,12 +5513,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,52%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,94%</t>
+          <t>30,53%</t>
         </is>
       </c>
     </row>
@@ -5541,12 +5541,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>134801</t>
+          <t>134252</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>158599</t>
+          <t>159241</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5556,12 +5556,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,19%</t>
+          <t>69,9%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>82,58%</t>
+          <t>82,91%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5576,12 +5576,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>127114</t>
+          <t>125627</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>152152</t>
+          <t>149674</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5591,12 +5591,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>78,19%</t>
+          <t>76,92%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5611,12 +5611,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>270877</t>
+          <t>268606</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>303718</t>
+          <t>303430</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5626,12 +5626,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>70,06%</t>
+          <t>69,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,48%</t>
         </is>
       </c>
     </row>
@@ -5771,12 +5771,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>61477</t>
+          <t>63327</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>94063</t>
+          <t>92605</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5786,12 +5786,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>25,33%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>37,63%</t>
+          <t>37,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5806,12 +5806,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>56727</t>
+          <t>57774</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>85236</t>
+          <t>86516</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5821,12 +5821,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>21,42%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>32,19%</t>
+          <t>32,67%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5841,12 +5841,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>128030</t>
+          <t>128163</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>168369</t>
+          <t>168871</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5856,12 +5856,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,87%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>32,71%</t>
+          <t>32,8%</t>
         </is>
       </c>
     </row>
@@ -5884,12 +5884,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>155910</t>
+          <t>157368</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>188496</t>
+          <t>186646</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5899,12 +5899,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,37%</t>
+          <t>62,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>74,67%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5919,12 +5919,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>179594</t>
+          <t>178314</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>208103</t>
+          <t>207056</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5934,12 +5934,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>67,81%</t>
+          <t>67,33%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>78,58%</t>
+          <t>78,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5954,12 +5954,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>346434</t>
+          <t>345932</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>386773</t>
+          <t>386640</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5969,12 +5969,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,2%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,13%</t>
+          <t>75,1%</t>
         </is>
       </c>
     </row>
@@ -6114,12 +6114,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>138788</t>
+          <t>137415</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>181847</t>
+          <t>182421</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6129,12 +6129,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,94%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6149,12 +6149,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>175658</t>
+          <t>176965</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>224370</t>
+          <t>224895</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6164,12 +6164,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>35,84%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6184,12 +6184,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>324334</t>
+          <t>326360</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>392241</t>
+          <t>392953</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6199,12 +6199,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,2%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>32,68%</t>
+          <t>32,74%</t>
         </is>
       </c>
     </row>
@@ -6227,12 +6227,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>392232</t>
+          <t>391658</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>435291</t>
+          <t>436664</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6242,12 +6242,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>75,82%</t>
+          <t>76,06%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6262,12 +6262,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>401617</t>
+          <t>401092</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>450329</t>
+          <t>449022</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6277,12 +6277,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>64,16%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>71,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6297,12 +6297,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>807824</t>
+          <t>807112</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>875731</t>
+          <t>873705</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6312,12 +6312,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>67,32%</t>
+          <t>67,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,97%</t>
+          <t>72,8%</t>
         </is>
       </c>
     </row>
@@ -6457,12 +6457,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>241641</t>
+          <t>238000</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>291250</t>
+          <t>289458</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6472,12 +6472,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6492,12 +6492,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>239914</t>
+          <t>239022</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>293906</t>
+          <t>292634</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6507,12 +6507,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>41,85%</t>
+          <t>41,67%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6527,12 +6527,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>495867</t>
+          <t>495221</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>565978</t>
+          <t>571515</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6542,12 +6542,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,06%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>42,36%</t>
+          <t>42,77%</t>
         </is>
       </c>
     </row>
@@ -6570,12 +6570,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>342655</t>
+          <t>344447</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>392264</t>
+          <t>395905</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6585,12 +6585,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,05%</t>
+          <t>54,34%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>61,88%</t>
+          <t>62,45%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6605,12 +6605,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>408388</t>
+          <t>409660</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>462380</t>
+          <t>463272</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6620,12 +6620,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>58,15%</t>
+          <t>58,33%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6640,12 +6640,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>770221</t>
+          <t>764684</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>840332</t>
+          <t>840978</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6655,12 +6655,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>57,64%</t>
+          <t>57,23%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,94%</t>
         </is>
       </c>
     </row>
@@ -6800,12 +6800,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>813097</t>
+          <t>810338</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>915239</t>
+          <t>915626</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6815,12 +6815,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>27,83%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,45%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6835,12 +6835,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>924557</t>
+          <t>925666</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1035890</t>
+          <t>1036465</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6850,12 +6850,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>29,37%</t>
+          <t>29,4%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>32,9%</t>
+          <t>32,92%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6870,12 +6870,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1772288</t>
+          <t>1778019</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1921758</t>
+          <t>1922867</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6885,12 +6885,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>29,25%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>31,71%</t>
+          <t>31,73%</t>
         </is>
       </c>
     </row>
@@ -6913,12 +6913,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1996367</t>
+          <t>1995980</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2098509</t>
+          <t>2101268</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6928,12 +6928,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,55%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>72,17%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6948,12 +6948,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2112412</t>
+          <t>2111837</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2223745</t>
+          <t>2222636</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6963,12 +6963,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>67,1%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>70,63%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6983,12 +6983,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4138150</t>
+          <t>4137041</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4287620</t>
+          <t>4281889</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6998,12 +6998,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>68,29%</t>
+          <t>68,27%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>70,66%</t>
         </is>
       </c>
     </row>
@@ -7379,12 +7379,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>43901</t>
+          <t>45580</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>71677</t>
+          <t>72220</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7394,12 +7394,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>29,23%</t>
+          <t>29,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7414,12 +7414,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>50774</t>
+          <t>50909</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>78877</t>
+          <t>78634</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7429,12 +7429,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>20,61%</t>
+          <t>20,67%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>32,02%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7449,12 +7449,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>102227</t>
+          <t>103263</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>141266</t>
+          <t>142734</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7464,12 +7464,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>21,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>28,74%</t>
+          <t>29,04%</t>
         </is>
       </c>
     </row>
@@ -7492,12 +7492,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>173541</t>
+          <t>172998</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>201317</t>
+          <t>199638</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7507,12 +7507,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>70,77%</t>
+          <t>70,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>81,41%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7527,12 +7527,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>167457</t>
+          <t>167700</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>195560</t>
+          <t>195425</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7542,12 +7542,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>67,98%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>79,39%</t>
+          <t>79,33%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7562,12 +7562,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>350285</t>
+          <t>348817</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>389324</t>
+          <t>388288</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7577,12 +7577,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>71,26%</t>
+          <t>70,96%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>78,99%</t>
         </is>
       </c>
     </row>
@@ -7722,12 +7722,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85713</t>
+          <t>86573</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>119145</t>
+          <t>122018</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7737,12 +7737,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>32,81%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>114942</t>
+          <t>114778</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>150897</t>
+          <t>152611</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7772,12 +7772,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>38,36%</t>
+          <t>38,8%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7792,12 +7792,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>208992</t>
+          <t>208092</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>260105</t>
+          <t>260243</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7807,12 +7807,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>27,63%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>34,38%</t>
+          <t>34,4%</t>
         </is>
       </c>
     </row>
@@ -7835,12 +7835,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>244020</t>
+          <t>241147</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>277452</t>
+          <t>276592</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7850,12 +7850,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>66,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,16%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>242430</t>
+          <t>240716</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>278385</t>
+          <t>278549</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7885,12 +7885,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>61,64%</t>
+          <t>61,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,78%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7905,12 +7905,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>496387</t>
+          <t>496249</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>547500</t>
+          <t>548400</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7920,12 +7920,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>65,62%</t>
+          <t>65,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,49%</t>
         </is>
       </c>
     </row>
@@ -8065,12 +8065,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>53295</t>
+          <t>53636</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>80300</t>
+          <t>79878</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8080,12 +8080,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>27,64%</t>
+          <t>27,5%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8100,12 +8100,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>63261</t>
+          <t>64187</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>95193</t>
+          <t>94048</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8115,12 +8115,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,86%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8135,12 +8135,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>121773</t>
+          <t>125643</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>164343</t>
+          <t>165330</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8150,12 +8150,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>21,0%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,63%</t>
         </is>
       </c>
     </row>
@@ -8178,12 +8178,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>210207</t>
+          <t>210629</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>237212</t>
+          <t>236871</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,5%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>81,65%</t>
+          <t>81,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>212571</t>
+          <t>213716</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>244503</t>
+          <t>243577</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8228,12 +8228,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,14%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8248,12 +8248,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>433927</t>
+          <t>432940</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>476497</t>
+          <t>472627</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8263,12 +8263,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>79,65%</t>
+          <t>79,0%</t>
         </is>
       </c>
     </row>
@@ -8408,12 +8408,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>67462</t>
+          <t>68911</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>99454</t>
+          <t>101105</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8423,12 +8423,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,88%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>30,13%</t>
+          <t>30,63%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8443,12 +8443,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>71994</t>
+          <t>71232</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>105046</t>
+          <t>104335</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8458,12 +8458,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>30,11%</t>
+          <t>29,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>149282</t>
+          <t>146140</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>193354</t>
+          <t>194610</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8493,12 +8493,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>21,53%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>28,48%</t>
+          <t>28,67%</t>
         </is>
       </c>
     </row>
@@ -8521,12 +8521,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>230593</t>
+          <t>228942</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>262585</t>
+          <t>261136</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8536,12 +8536,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>69,37%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,12%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8556,12 +8556,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>243815</t>
+          <t>244526</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>276867</t>
+          <t>277629</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8571,12 +8571,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>69,89%</t>
+          <t>70,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,58%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>485554</t>
+          <t>484298</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>529626</t>
+          <t>532768</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8606,12 +8606,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,52%</t>
+          <t>71,33%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>78,01%</t>
+          <t>78,47%</t>
         </is>
       </c>
     </row>
@@ -8751,12 +8751,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69259</t>
+          <t>70579</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>89806</t>
+          <t>90045</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8766,12 +8766,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>58,09%</t>
+          <t>59,2%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>75,33%</t>
+          <t>75,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8786,12 +8786,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>89520</t>
+          <t>89564</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>111066</t>
+          <t>111094</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8801,12 +8801,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>61,53%</t>
+          <t>61,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,35%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8821,12 +8821,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>166474</t>
+          <t>165363</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>196722</t>
+          <t>195245</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8836,12 +8836,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>62,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>74,31%</t>
+          <t>73,75%</t>
         </is>
       </c>
     </row>
@@ -8864,12 +8864,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>29416</t>
+          <t>29177</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>49963</t>
+          <t>48643</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8879,12 +8879,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>24,67%</t>
+          <t>24,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>40,8%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8899,12 +8899,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>34434</t>
+          <t>34406</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>55980</t>
+          <t>55936</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8914,12 +8914,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>38,47%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8934,12 +8934,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>68000</t>
+          <t>69477</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>98248</t>
+          <t>99359</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8949,12 +8949,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>25,69%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>37,11%</t>
+          <t>37,53%</t>
         </is>
       </c>
     </row>
@@ -9094,12 +9094,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>41812</t>
+          <t>42841</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>69076</t>
+          <t>68162</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9109,12 +9109,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,9%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9129,12 +9129,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>63540</t>
+          <t>64270</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>93708</t>
+          <t>94218</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9144,12 +9144,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>26,01%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>37,92%</t>
+          <t>38,12%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>112757</t>
+          <t>111691</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>153317</t>
+          <t>151714</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9179,12 +9179,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>23,45%</t>
+          <t>23,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,56%</t>
         </is>
       </c>
     </row>
@@ -9207,12 +9207,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>164539</t>
+          <t>165453</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>191803</t>
+          <t>190774</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9222,12 +9222,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>70,43%</t>
+          <t>70,82%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>82,1%</t>
+          <t>81,66%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9242,12 +9242,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>153429</t>
+          <t>152919</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>183597</t>
+          <t>182867</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9257,12 +9257,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,08%</t>
+          <t>61,88%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,29%</t>
+          <t>73,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9277,12 +9277,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>327436</t>
+          <t>329039</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>367996</t>
+          <t>369062</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9292,12 +9292,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>68,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>76,55%</t>
+          <t>76,77%</t>
         </is>
       </c>
     </row>
@@ -9437,12 +9437,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>121940</t>
+          <t>122634</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>163329</t>
+          <t>163527</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9452,12 +9452,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>27,73%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,97%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9472,12 +9472,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>145710</t>
+          <t>144923</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>187825</t>
+          <t>187591</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9487,12 +9487,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>29,92%</t>
+          <t>29,76%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,56%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9507,12 +9507,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>281393</t>
+          <t>279553</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>339273</t>
+          <t>341433</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9522,12 +9522,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>30,28%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>36,51%</t>
+          <t>36,74%</t>
         </is>
       </c>
     </row>
@@ -9550,12 +9550,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>278978</t>
+          <t>278780</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>320367</t>
+          <t>319673</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9565,12 +9565,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>63,03%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>72,27%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9585,12 +9585,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>299226</t>
+          <t>299460</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>341341</t>
+          <t>342128</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9600,12 +9600,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>61,44%</t>
+          <t>61,48%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>70,08%</t>
+          <t>70,24%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9620,12 +9620,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>590085</t>
+          <t>587925</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>647965</t>
+          <t>649805</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9635,12 +9635,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>63,49%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>69,72%</t>
+          <t>69,92%</t>
         </is>
       </c>
     </row>
@@ -9780,12 +9780,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>314079</t>
+          <t>314734</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>363338</t>
+          <t>365989</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9795,12 +9795,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>49,06%</t>
+          <t>49,16%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>56,75%</t>
+          <t>57,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9815,12 +9815,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>335949</t>
+          <t>330951</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>390471</t>
+          <t>387346</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9830,12 +9830,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9850,12 +9850,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>661181</t>
+          <t>660705</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>737249</t>
+          <t>732803</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9865,12 +9865,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>49,65%</t>
+          <t>49,62%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>55,37%</t>
+          <t>55,03%</t>
         </is>
       </c>
     </row>
@@ -9893,12 +9893,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>276914</t>
+          <t>274263</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>326173</t>
+          <t>325518</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9908,12 +9908,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>43,25%</t>
+          <t>42,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>50,94%</t>
+          <t>50,84%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9928,12 +9928,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>300870</t>
+          <t>303995</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>355392</t>
+          <t>360390</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9943,12 +9943,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>43,97%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>51,41%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9963,12 +9963,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>594344</t>
+          <t>598790</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>670412</t>
+          <t>670888</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9978,12 +9978,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>44,63%</t>
+          <t>44,97%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>50,35%</t>
+          <t>50,38%</t>
         </is>
       </c>
     </row>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>877134</t>
+          <t>878313</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>974335</t>
+          <t>979996</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,97%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>36,57%</t>
+          <t>36,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10158,12 +10158,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1011762</t>
+          <t>1011202</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>1112294</t>
+          <t>1118218</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10173,12 +10173,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,27%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>38,79%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10193,12 +10193,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1924967</t>
+          <t>1924204</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>2070108</t>
+          <t>2069709</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10208,7 +10208,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,79%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1689998</t>
+          <t>1684337</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>1787199</t>
+          <t>1786020</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>67,08%</t>
+          <t>67,03%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1755021</t>
+          <t>1749097</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1855553</t>
+          <t>1856113</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10286,12 +10286,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>61,21%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,73%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10306,12 +10306,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3461540</t>
+          <t>3461939</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>3606681</t>
+          <t>3607444</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10326,7 +10326,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,21%</t>
         </is>
       </c>
     </row>
@@ -10697,32 +10697,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>146886</t>
+          <t>141477</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>123484</t>
+          <t>123408</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>166878</t>
+          <t>158441</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>48,09%</t>
+          <t>47,02%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>40,43%</t>
+          <t>41,01%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>54,64%</t>
+          <t>52,65%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10732,32 +10732,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>130754</t>
+          <t>147865</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>117461</t>
+          <t>133559</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>146205</t>
+          <t>163170</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>45,46%</t>
+          <t>47,78%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>43,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,83%</t>
+          <t>52,73%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -10767,32 +10767,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>277640</t>
+          <t>289342</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>251861</t>
+          <t>266445</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>304290</t>
+          <t>313787</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>47,4%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>51,31%</t>
+          <t>51,41%</t>
         </is>
       </c>
     </row>
@@ -10810,32 +10810,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>158544</t>
+          <t>159440</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>138552</t>
+          <t>142476</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>181946</t>
+          <t>177509</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>51,91%</t>
+          <t>52,98%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>59,57%</t>
+          <t>58,99%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -10845,32 +10845,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>156853</t>
+          <t>161599</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>141402</t>
+          <t>146294</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>170146</t>
+          <t>175905</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>54,54%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>47,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>59,16%</t>
+          <t>56,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -10880,32 +10880,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>315397</t>
+          <t>321039</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>288747</t>
+          <t>296594</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>341176</t>
+          <t>343936</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>52,6%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>48,69%</t>
+          <t>48,59%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>56,35%</t>
         </is>
       </c>
     </row>
@@ -10923,17 +10923,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>305430</t>
+          <t>300917</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>305430</t>
+          <t>300917</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>305430</t>
+          <t>300917</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -10958,17 +10958,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>287607</t>
+          <t>309464</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>287607</t>
+          <t>309464</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>287607</t>
+          <t>309464</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -10993,17 +10993,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>593037</t>
+          <t>610381</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>593037</t>
+          <t>610381</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>593037</t>
+          <t>610381</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11040,32 +11040,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>190856</t>
+          <t>190742</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>162301</t>
+          <t>159052</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>220625</t>
+          <t>216906</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>37,65%</t>
+          <t>36,82%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>32,01%</t>
+          <t>30,7%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,52%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11075,32 +11075,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>178033</t>
+          <t>187994</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>158915</t>
+          <t>168205</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>197814</t>
+          <t>207869</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>35,36%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>31,68%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11110,32 +11110,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>368889</t>
+          <t>378737</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>332627</t>
+          <t>344462</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>405496</t>
+          <t>415992</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>36,58%</t>
+          <t>36,08%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>32,98%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>40,21%</t>
+          <t>39,63%</t>
         </is>
       </c>
     </row>
@@ -11153,32 +11153,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>316128</t>
+          <t>327286</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>286359</t>
+          <t>301122</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>344683</t>
+          <t>358976</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>62,35%</t>
+          <t>63,18%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>56,48%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>69,3%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -11188,32 +11188,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>323515</t>
+          <t>343618</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>303734</t>
+          <t>323743</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>342633</t>
+          <t>363407</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>64,64%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>60,56%</t>
+          <t>60,9%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>68,32%</t>
+          <t>68,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11223,32 +11223,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>639643</t>
+          <t>670903</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>603036</t>
+          <t>633648</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>675905</t>
+          <t>705178</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>63,42%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>60,37%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>67,02%</t>
+          <t>67,18%</t>
         </is>
       </c>
     </row>
@@ -11266,17 +11266,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>506984</t>
+          <t>518028</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>506984</t>
+          <t>518028</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>506984</t>
+          <t>518028</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -11301,17 +11301,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>501548</t>
+          <t>531612</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>501548</t>
+          <t>531612</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>501548</t>
+          <t>531612</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -11336,17 +11336,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>1008532</t>
+          <t>1049640</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1008532</t>
+          <t>1049640</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1008532</t>
+          <t>1049640</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -11383,32 +11383,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>70826</t>
+          <t>69426</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>57661</t>
+          <t>55919</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>85947</t>
+          <t>84151</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>23,59%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>19,21%</t>
+          <t>18,68%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>28,63%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -11418,32 +11418,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>90508</t>
+          <t>90507</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>76415</t>
+          <t>77124</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>106582</t>
+          <t>105059</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>27,0%</t>
+          <t>26,49%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,57%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>30,75%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -11453,32 +11453,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>161334</t>
+          <t>159933</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>140875</t>
+          <t>140697</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>182322</t>
+          <t>180666</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>25,39%</t>
+          <t>24,95%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,17%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>28,69%</t>
+          <t>28,18%</t>
         </is>
       </c>
     </row>
@@ -11496,32 +11496,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>229401</t>
+          <t>229883</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>214280</t>
+          <t>215158</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>242566</t>
+          <t>243390</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>76,41%</t>
+          <t>76,8%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,88%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>80,79%</t>
+          <t>81,32%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11531,32 +11531,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>244767</t>
+          <t>251198</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>228693</t>
+          <t>236646</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>258860</t>
+          <t>264581</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>73,0%</t>
+          <t>73,51%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>69,25%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,43%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11566,32 +11566,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>474168</t>
+          <t>481080</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>453180</t>
+          <t>460347</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>494627</t>
+          <t>500316</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>74,61%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,82%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,83%</t>
+          <t>78,05%</t>
         </is>
       </c>
     </row>
@@ -11609,17 +11609,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>300227</t>
+          <t>299309</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>300227</t>
+          <t>299309</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>300227</t>
+          <t>299309</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11644,17 +11644,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>335275</t>
+          <t>341705</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>335275</t>
+          <t>341705</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>335275</t>
+          <t>341705</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11679,17 +11679,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>635502</t>
+          <t>641013</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>635502</t>
+          <t>641013</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>635502</t>
+          <t>641013</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11726,32 +11726,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>155961</t>
+          <t>185786</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>134519</t>
+          <t>159128</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>178966</t>
+          <t>209280</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>42,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -11761,32 +11761,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>176231</t>
+          <t>197614</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>108972</t>
+          <t>177658</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>223590</t>
+          <t>218390</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>47,09%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>47,22%</t>
+          <t>52,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -11796,32 +11796,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>332191</t>
+          <t>383400</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>240616</t>
+          <t>351226</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>384655</t>
+          <t>416345</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>42,39%</t>
+          <t>48,51%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>49,09%</t>
+          <t>52,68%</t>
         </is>
       </c>
     </row>
@@ -11839,32 +11839,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>154159</t>
+          <t>184952</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>131154</t>
+          <t>161458</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>175601</t>
+          <t>211610</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>43,55%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>56,62%</t>
+          <t>57,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -11874,32 +11874,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>297234</t>
+          <t>221999</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>249875</t>
+          <t>201223</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>364493</t>
+          <t>241955</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>52,78%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -11909,32 +11909,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>451394</t>
+          <t>406951</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>398930</t>
+          <t>374006</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>542969</t>
+          <t>439125</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>51,49%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>50,91%</t>
+          <t>47,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>69,29%</t>
+          <t>55,56%</t>
         </is>
       </c>
     </row>
@@ -11952,17 +11952,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>310120</t>
+          <t>370738</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>310120</t>
+          <t>370738</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>310120</t>
+          <t>370738</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -11987,17 +11987,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>473465</t>
+          <t>419613</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>473465</t>
+          <t>419613</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>473465</t>
+          <t>419613</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12022,17 +12022,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>783585</t>
+          <t>790351</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>783585</t>
+          <t>790351</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>783585</t>
+          <t>790351</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12069,32 +12069,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>146656</t>
+          <t>162063</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>139221</t>
+          <t>153631</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>152903</t>
+          <t>169788</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>85,61%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>81,16%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>90,78%</t>
+          <t>89,69%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12104,32 +12104,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>178082</t>
+          <t>193369</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>171056</t>
+          <t>184448</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>183979</t>
+          <t>199094</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>88,03%</t>
+          <t>87,97%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,95%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -12139,32 +12139,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>324738</t>
+          <t>355433</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>315087</t>
+          <t>344256</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>334087</t>
+          <t>365078</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>87,6%</t>
+          <t>86,88%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,99%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>89,24%</t>
         </is>
       </c>
     </row>
@@ -12182,32 +12182,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>21773</t>
+          <t>27236</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15526</t>
+          <t>19511</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>29208</t>
+          <t>35668</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>12,93%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>10,31%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -12217,32 +12217,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>24210</t>
+          <t>26433</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18313</t>
+          <t>20708</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>31236</t>
+          <t>35354</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>11,97%</t>
+          <t>12,03%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -12252,32 +12252,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>45983</t>
+          <t>53668</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>36634</t>
+          <t>44023</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>55634</t>
+          <t>64845</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>13,12%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>15,85%</t>
         </is>
       </c>
     </row>
@@ -12295,17 +12295,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>168429</t>
+          <t>189299</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>168429</t>
+          <t>189299</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>168429</t>
+          <t>189299</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12330,17 +12330,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>202292</t>
+          <t>219802</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>202292</t>
+          <t>219802</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>202292</t>
+          <t>219802</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12365,17 +12365,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>370721</t>
+          <t>409101</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>370721</t>
+          <t>409101</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>370721</t>
+          <t>409101</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12412,32 +12412,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>45792</t>
+          <t>44075</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>34420</t>
+          <t>33691</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>57832</t>
+          <t>57021</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>18,05%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12447,32 +12447,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>49696</t>
+          <t>50045</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>40466</t>
+          <t>40708</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>59720</t>
+          <t>61336</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,43%</t>
+          <t>16,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>24,24%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12482,32 +12482,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>95488</t>
+          <t>94120</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>79594</t>
+          <t>80242</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>111751</t>
+          <t>110290</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>15,92%</t>
+          <t>16,01%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,35%</t>
+          <t>22,0%</t>
         </is>
       </c>
     </row>
@@ -12525,32 +12525,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>207940</t>
+          <t>205660</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>195900</t>
+          <t>192714</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>219312</t>
+          <t>216044</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>81,95%</t>
+          <t>82,35%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>77,21%</t>
+          <t>77,17%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>86,43%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12560,32 +12560,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>196654</t>
+          <t>201515</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>186630</t>
+          <t>190224</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>205884</t>
+          <t>210852</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>80,11%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>75,76%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,57%</t>
+          <t>83,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12595,32 +12595,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>404594</t>
+          <t>407174</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>388331</t>
+          <t>391004</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>420488</t>
+          <t>421052</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>81,22%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>77,65%</t>
+          <t>78,0%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,08%</t>
+          <t>83,99%</t>
         </is>
       </c>
     </row>
@@ -12638,17 +12638,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>253732</t>
+          <t>249735</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>253732</t>
+          <t>249735</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>253732</t>
+          <t>249735</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12673,17 +12673,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>246350</t>
+          <t>251560</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>246350</t>
+          <t>251560</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>246350</t>
+          <t>251560</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12708,17 +12708,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>500082</t>
+          <t>501294</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>500082</t>
+          <t>501294</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>500082</t>
+          <t>501294</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12755,32 +12755,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>283080</t>
+          <t>322414</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>253688</t>
+          <t>292544</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>311207</t>
+          <t>352906</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>47,15%</t>
+          <t>46,15%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>51,83%</t>
+          <t>50,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -12790,32 +12790,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>494480</t>
+          <t>337285</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>375999</t>
+          <t>312230</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>682808</t>
+          <t>364023</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>59,69%</t>
+          <t>45,49%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>45,39%</t>
+          <t>42,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -12825,32 +12825,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>777561</t>
+          <t>659699</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>656983</t>
+          <t>620456</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1022653</t>
+          <t>700712</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>45,81%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>45,98%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,58%</t>
+          <t>48,66%</t>
         </is>
       </c>
     </row>
@@ -12868,32 +12868,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>317319</t>
+          <t>376217</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>289192</t>
+          <t>345725</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>346711</t>
+          <t>406087</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>53,85%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>48,17%</t>
+          <t>49,49%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -12903,32 +12903,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>333885</t>
+          <t>404101</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>145557</t>
+          <t>377363</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>452366</t>
+          <t>429156</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>40,31%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>54,61%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -12938,32 +12938,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>651204</t>
+          <t>780319</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>406112</t>
+          <t>739306</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>771782</t>
+          <t>819562</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>54,19%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,42%</t>
+          <t>51,34%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>54,02%</t>
+          <t>56,91%</t>
         </is>
       </c>
     </row>
@@ -12981,17 +12981,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>600399</t>
+          <t>698631</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>600399</t>
+          <t>698631</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>600399</t>
+          <t>698631</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13016,17 +13016,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>828365</t>
+          <t>741386</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>828365</t>
+          <t>741386</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>828365</t>
+          <t>741386</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13051,17 +13051,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>1428765</t>
+          <t>1440018</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>1428765</t>
+          <t>1440018</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>1428765</t>
+          <t>1440018</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13098,32 +13098,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>420558</t>
+          <t>486282</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>196693</t>
+          <t>458874</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>586079</t>
+          <t>514709</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>46,28%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,65%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>64,5%</t>
+          <t>66,75%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13133,22 +13133,22 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>484425</t>
+          <t>558885</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>464060</t>
+          <t>534130</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>506712</t>
+          <t>580093</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>68,82%</t>
+          <t>68,97%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
@@ -13158,7 +13158,7 @@
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>71,98%</t>
+          <t>71,59%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13168,32 +13168,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>904983</t>
+          <t>1045167</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>572801</t>
+          <t>1013528</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1078453</t>
+          <t>1082018</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>56,12%</t>
+          <t>66,09%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>35,52%</t>
+          <t>64,09%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>66,88%</t>
+          <t>68,42%</t>
         </is>
       </c>
     </row>
@@ -13211,32 +13211,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>488081</t>
+          <t>284768</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>322560</t>
+          <t>256341</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>711946</t>
+          <t>312176</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>53,72%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>35,5%</t>
+          <t>33,25%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>78,35%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13246,27 +13246,27 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>219499</t>
+          <t>251422</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>197212</t>
+          <t>230214</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>239864</t>
+          <t>276177</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>31,18%</t>
+          <t>31,03%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
@@ -13281,32 +13281,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>707580</t>
+          <t>536190</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>534110</t>
+          <t>499339</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1039762</t>
+          <t>567829</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>43,88%</t>
+          <t>33,91%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>31,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>64,48%</t>
+          <t>35,91%</t>
         </is>
       </c>
     </row>
@@ -13324,17 +13324,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>908639</t>
+          <t>771050</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>908639</t>
+          <t>771050</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>908639</t>
+          <t>771050</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13359,17 +13359,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>703924</t>
+          <t>810307</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>703924</t>
+          <t>810307</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>703924</t>
+          <t>810307</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13394,17 +13394,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1612563</t>
+          <t>1581357</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1612563</t>
+          <t>1581357</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1612563</t>
+          <t>1581357</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13441,32 +13441,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>1460614</t>
+          <t>1602266</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>1140942</t>
+          <t>1534252</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>1588859</t>
+          <t>1669016</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>43,55%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>45,16%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>47,37%</t>
+          <t>49,12%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13476,32 +13476,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>1782210</t>
+          <t>1763564</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>1639898</t>
+          <t>1713086</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>2089353</t>
+          <t>1816654</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>49,8%</t>
+          <t>48,64%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>45,82%</t>
+          <t>47,25%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>58,38%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13511,32 +13511,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>3242824</t>
+          <t>3365829</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>2925284</t>
+          <t>3272423</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>3527322</t>
+          <t>3448444</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>46,78%</t>
+          <t>47,92%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>42,19%</t>
+          <t>46,59%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>50,88%</t>
+          <t>49,1%</t>
         </is>
       </c>
     </row>
@@ -13554,32 +13554,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1893346</t>
+          <t>1795441</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1765101</t>
+          <t>1728691</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2213018</t>
+          <t>1863455</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>52,84%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>52,63%</t>
+          <t>50,88%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>65,98%</t>
+          <t>54,84%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13589,32 +13589,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>1796617</t>
+          <t>1861884</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1489474</t>
+          <t>1808794</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>1938929</t>
+          <t>1912362</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>50,2%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>54,18%</t>
+          <t>52,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13624,32 +13624,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>3689963</t>
+          <t>3657326</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3405465</t>
+          <t>3574711</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>4007503</t>
+          <t>3750732</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>53,22%</t>
+          <t>52,08%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>49,12%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>57,81%</t>
+          <t>53,41%</t>
         </is>
       </c>
     </row>
@@ -13667,17 +13667,17 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>3353960</t>
+          <t>3397707</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>3353960</t>
+          <t>3397707</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>3353960</t>
+          <t>3397707</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13702,17 +13702,17 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>3578827</t>
+          <t>3625448</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13737,17 +13737,17 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>6932787</t>
+          <t>7023155</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>6932787</t>
+          <t>7023155</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6932787</t>
+          <t>7023155</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
